--- a/X-Series/XD12R/Jig/XCR_XDR/XC24RV_XD12RV/Docs/GT/XCR_TEST_PLAN_260624.xlsx
+++ b/X-Series/XD12R/Jig/XCR_XDR/XC24RV_XD12RV/Docs/GT/XCR_TEST_PLAN_260624.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\FW\X-Series\XD12R\Jig\XCR_XDR\XC24RV_XD12RV\Docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\FW\X-Series\XD12R\Jig\XCR_XDR\XC24RV_XD12RV\Docs\GT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA5951E1-D4AF-4448-A279-EF5339A52295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91D31B1-4591-4DDA-AAF7-6DACBE9ED82F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="86295" yWindow="2280" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test_Plan" sheetId="2" r:id="rId1"/>
@@ -2973,6 +2973,9 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3008,9 +3011,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3303,12 +3303,12 @@
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
     <col min="2" max="3" width="16.25" customWidth="1"/>
     <col min="4" max="4" width="21" customWidth="1"/>
-    <col min="5" max="5" width="16.25" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="28.33203125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="14.4140625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="24.4140625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="17.33203125" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="34.9140625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="16.25" customWidth="1"/>
+    <col min="6" max="6" width="28.33203125" customWidth="1"/>
+    <col min="7" max="7" width="14.4140625" customWidth="1"/>
+    <col min="8" max="8" width="24.4140625" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" customWidth="1"/>
+    <col min="10" max="10" width="34.9140625" customWidth="1"/>
     <col min="11" max="11" width="25.5" customWidth="1"/>
     <col min="12" max="12" width="25.75" customWidth="1"/>
     <col min="13" max="13" width="41.4140625" customWidth="1"/>
@@ -3322,7 +3322,7 @@
   <sheetData>
     <row r="2" spans="1:13" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="3" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B3" s="79" t="s">
+      <c r="B3" s="80" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -3360,7 +3360,7 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="29.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="80"/>
+      <c r="B4" s="81"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6" t="s">
         <v>12</v>
@@ -3378,7 +3378,7 @@
       <c r="M4" s="8"/>
     </row>
     <row r="5" spans="1:13" ht="110" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B5" s="80"/>
+      <c r="B5" s="81"/>
       <c r="C5" s="5" t="s">
         <v>14</v>
       </c>
@@ -3398,7 +3398,7 @@
       <c r="M5" s="8"/>
     </row>
     <row r="6" spans="1:13" ht="37" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="80"/>
+      <c r="B6" s="81"/>
       <c r="C6" s="9">
         <v>1</v>
       </c>
@@ -3435,7 +3435,7 @@
     </row>
     <row r="7" spans="1:13" ht="86" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="15"/>
-      <c r="B7" s="80"/>
+      <c r="B7" s="81"/>
       <c r="C7" s="16">
         <v>2</v>
       </c>
@@ -3457,7 +3457,7 @@
       <c r="I7" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="91" t="s">
+      <c r="J7" s="79" t="s">
         <v>127</v>
       </c>
       <c r="K7" s="18" t="s">
@@ -3472,7 +3472,7 @@
     </row>
     <row r="8" spans="1:13" ht="101.5" x14ac:dyDescent="0.45">
       <c r="A8" s="15"/>
-      <c r="B8" s="80"/>
+      <c r="B8" s="81"/>
       <c r="C8" s="16">
         <v>3</v>
       </c>
@@ -3509,7 +3509,7 @@
     </row>
     <row r="9" spans="1:13" ht="101.5" x14ac:dyDescent="0.45">
       <c r="A9" s="15"/>
-      <c r="B9" s="80"/>
+      <c r="B9" s="81"/>
       <c r="C9" s="16">
         <v>4</v>
       </c>
@@ -3546,7 +3546,7 @@
     </row>
     <row r="10" spans="1:13" ht="101.5" x14ac:dyDescent="0.45">
       <c r="A10" s="15"/>
-      <c r="B10" s="80"/>
+      <c r="B10" s="81"/>
       <c r="C10" s="16">
         <v>5</v>
       </c>
@@ -3583,7 +3583,7 @@
     </row>
     <row r="11" spans="1:13" ht="58" x14ac:dyDescent="0.45">
       <c r="A11" s="15"/>
-      <c r="B11" s="80"/>
+      <c r="B11" s="81"/>
       <c r="C11" s="16">
         <v>6</v>
       </c>
@@ -3608,7 +3608,7 @@
       <c r="J11" s="78" t="s">
         <v>121</v>
       </c>
-      <c r="K11" s="91" t="s">
+      <c r="K11" s="79" t="s">
         <v>128</v>
       </c>
       <c r="L11" s="17" t="s">
@@ -3618,7 +3618,7 @@
     </row>
     <row r="12" spans="1:13" ht="133.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="15"/>
-      <c r="B12" s="80"/>
+      <c r="B12" s="81"/>
       <c r="C12" s="16">
         <v>7</v>
       </c>
@@ -3653,7 +3653,7 @@
     </row>
     <row r="13" spans="1:13" ht="132" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="15"/>
-      <c r="B13" s="80"/>
+      <c r="B13" s="81"/>
       <c r="C13" s="16">
         <v>8</v>
       </c>
@@ -3687,7 +3687,7 @@
       <c r="M13" s="21"/>
     </row>
     <row r="14" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B14" s="81"/>
+      <c r="B14" s="82"/>
       <c r="C14" s="22">
         <v>9</v>
       </c>
@@ -3737,7 +3737,7 @@
       <c r="M16" s="27"/>
     </row>
     <row r="17" spans="2:13" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B17" s="79" t="s">
+      <c r="B17" s="80" t="s">
         <v>57</v>
       </c>
       <c r="C17" s="5" t="s">
@@ -3775,7 +3775,7 @@
       </c>
     </row>
     <row r="18" spans="2:13" ht="80" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B18" s="80"/>
+      <c r="B18" s="81"/>
       <c r="C18" s="5" t="s">
         <v>14</v>
       </c>
@@ -3795,7 +3795,7 @@
       <c r="M18" s="8"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B19" s="80"/>
+      <c r="B19" s="81"/>
       <c r="C19" s="9">
         <v>1</v>
       </c>
@@ -3821,7 +3821,7 @@
       <c r="M19" s="31"/>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B20" s="80"/>
+      <c r="B20" s="81"/>
       <c r="C20" s="16">
         <v>2</v>
       </c>
@@ -3849,7 +3849,7 @@
       <c r="M20" s="20"/>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B21" s="80"/>
+      <c r="B21" s="81"/>
       <c r="C21" s="16">
         <v>3</v>
       </c>
@@ -3875,7 +3875,7 @@
       <c r="M21" s="20"/>
     </row>
     <row r="22" spans="2:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B22" s="80"/>
+      <c r="B22" s="81"/>
       <c r="C22" s="34">
         <v>4</v>
       </c>
@@ -3901,7 +3901,7 @@
       <c r="M22" s="38"/>
     </row>
     <row r="23" spans="2:13" ht="44" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B23" s="80"/>
+      <c r="B23" s="81"/>
       <c r="C23" s="39"/>
       <c r="D23" s="40" t="s">
         <v>72</v>
@@ -3921,7 +3921,7 @@
       <c r="M23" s="44"/>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B24" s="82"/>
+      <c r="B24" s="83"/>
       <c r="C24" s="9">
         <v>5</v>
       </c>
@@ -3947,7 +3947,7 @@
       <c r="M24" s="31"/>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B25" s="82"/>
+      <c r="B25" s="83"/>
       <c r="C25" s="16">
         <v>6</v>
       </c>
@@ -3975,7 +3975,7 @@
       <c r="M25" s="20"/>
     </row>
     <row r="26" spans="2:13" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B26" s="82"/>
+      <c r="B26" s="83"/>
       <c r="C26" s="46"/>
       <c r="D26" s="47" t="s">
         <v>78</v>
@@ -3995,7 +3995,7 @@
       <c r="M26" s="51"/>
     </row>
     <row r="27" spans="2:13" ht="37" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B27" s="82"/>
+      <c r="B27" s="83"/>
       <c r="C27" s="39"/>
       <c r="D27" s="40" t="s">
         <v>80</v>
@@ -4015,7 +4015,7 @@
       <c r="M27" s="44"/>
     </row>
     <row r="28" spans="2:13" ht="29" x14ac:dyDescent="0.45">
-      <c r="B28" s="82"/>
+      <c r="B28" s="83"/>
       <c r="C28" s="16">
         <v>2</v>
       </c>
@@ -4047,7 +4047,7 @@
       <c r="M28" s="54"/>
     </row>
     <row r="29" spans="2:13" ht="43.5" x14ac:dyDescent="0.45">
-      <c r="B29" s="82"/>
+      <c r="B29" s="83"/>
       <c r="C29" s="16">
         <v>3</v>
       </c>
@@ -4077,7 +4077,7 @@
       <c r="M29" s="20"/>
     </row>
     <row r="30" spans="2:13" ht="43.5" x14ac:dyDescent="0.45">
-      <c r="B30" s="82"/>
+      <c r="B30" s="83"/>
       <c r="C30" s="16">
         <v>4</v>
       </c>
@@ -4107,7 +4107,7 @@
       <c r="M30" s="20"/>
     </row>
     <row r="31" spans="2:13" ht="240.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B31" s="82"/>
+      <c r="B31" s="83"/>
       <c r="C31" s="16">
         <v>11</v>
       </c>
@@ -4139,7 +4139,7 @@
       <c r="M31" s="21"/>
     </row>
     <row r="32" spans="2:13" ht="237.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B32" s="82"/>
+      <c r="B32" s="83"/>
       <c r="C32" s="16">
         <v>12</v>
       </c>
@@ -4171,7 +4171,7 @@
       <c r="M32" s="21"/>
     </row>
     <row r="33" spans="2:13" ht="119" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B33" s="82"/>
+      <c r="B33" s="83"/>
       <c r="C33" s="16">
         <v>13</v>
       </c>
@@ -4203,7 +4203,7 @@
       <c r="M33" s="19"/>
     </row>
     <row r="34" spans="2:13" ht="125" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B34" s="83"/>
+      <c r="B34" s="84"/>
       <c r="C34" s="46">
         <v>14</v>
       </c>
@@ -4283,7 +4283,7 @@
       <c r="M36" s="73"/>
     </row>
     <row r="37" spans="2:13" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B37" s="84" t="s">
+      <c r="B37" s="85" t="s">
         <v>110</v>
       </c>
       <c r="C37" s="9">
@@ -4310,12 +4310,12 @@
       <c r="L37" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="M37" s="85" t="s">
+      <c r="M37" s="86" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B38" s="82"/>
+      <c r="B38" s="83"/>
       <c r="C38" s="16">
         <v>23</v>
       </c>
@@ -4342,10 +4342,10 @@
       <c r="L38" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="M38" s="86"/>
+      <c r="M38" s="87"/>
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B39" s="82"/>
+      <c r="B39" s="83"/>
       <c r="C39" s="16">
         <v>24</v>
       </c>
@@ -4372,10 +4372,10 @@
       <c r="L39" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="M39" s="86"/>
+      <c r="M39" s="87"/>
     </row>
     <row r="40" spans="2:13" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B40" s="82"/>
+      <c r="B40" s="83"/>
       <c r="C40" s="16">
         <v>25</v>
       </c>
@@ -4402,10 +4402,10 @@
       <c r="L40" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="M40" s="86"/>
+      <c r="M40" s="87"/>
     </row>
     <row r="41" spans="2:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B41" s="83"/>
+      <c r="B41" s="84"/>
       <c r="C41" s="46">
         <v>26</v>
       </c>
@@ -4432,17 +4432,17 @@
       <c r="L41" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="M41" s="87"/>
+      <c r="M41" s="88"/>
     </row>
     <row r="86" spans="3:15" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="C86" s="88"/>
-      <c r="D86" s="89"/>
-      <c r="E86" s="89"/>
-      <c r="F86" s="89"/>
-      <c r="G86" s="89"/>
-      <c r="H86" s="89"/>
-      <c r="I86" s="89"/>
-      <c r="J86" s="90"/>
+      <c r="C86" s="89"/>
+      <c r="D86" s="90"/>
+      <c r="E86" s="90"/>
+      <c r="F86" s="90"/>
+      <c r="G86" s="90"/>
+      <c r="H86" s="90"/>
+      <c r="I86" s="90"/>
+      <c r="J86" s="91"/>
       <c r="K86" s="26"/>
       <c r="L86" s="26"/>
       <c r="M86" s="26"/>
